--- a/artfynd/A 1188-2026 artfynd.xlsx
+++ b/artfynd/A 1188-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118045797</v>
+        <v>126269252</v>
       </c>
       <c r="B2" t="n">
-        <v>97766</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övergården, Vrm</t>
+          <t>Värmlandnäs, Botilsäter, S 536, Övergården, vid infartsväg, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>391134</v>
+        <v>391167</v>
       </c>
       <c r="R2" t="n">
-        <v>6548414</v>
+        <v>6548308</v>
       </c>
       <c r="S2" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:57</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>8 blommande stänglar på västra sidan av vägen. Växer i hela vägområdet.</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,21 +758,392 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Innerslänt; nyligen dikat</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mats Lindqvist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mats Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga järnvägsmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118045729</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Övergården, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>391162</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6548335</v>
+      </c>
+      <c r="S3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Botilsäter</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sex blommande stänglar, växer i hela vägområdet. Östra sidan av vägen</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Åsa Tengström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Elvira Ljungberg, Åsa Tengström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åsa Tengström, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118045958</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Övergården, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>391184</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6548489</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Botilsäter</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med svinrot på båda sidor väg, i hela vägområdet, från punkten och ca 200 m söderut</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Tengström, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118045797</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Övergården, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>391134</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6548414</v>
+      </c>
+      <c r="S5" t="n">
+        <v>24</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Botilsäter</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>8 blommande stänglar på västra sidan av vägen. Växer i hela vägområdet.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Tengström, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 1188-2026 artfynd.xlsx
+++ b/artfynd/A 1188-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118045958</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Trafikverkets inventeringar av arter i statliga järnvägsmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126269252</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118045729</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,8 +1168,19 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118045797</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>